--- a/artfynd/A 14042-2023 artfynd.xlsx
+++ b/artfynd/A 14042-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14042-2023 artfynd.xlsx
+++ b/artfynd/A 14042-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1136,6 +1136,113 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>114365691</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96509</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Björnareåsens NR, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>331580</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6406504</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Partille</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Partille</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-01-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-01-23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tim Hipkiss</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tim Hipkiss</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14042-2023 artfynd.xlsx
+++ b/artfynd/A 14042-2023 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>92750691</v>
+        <v>87293074</v>
       </c>
       <c r="B3" t="n">
-        <v>95519</v>
+        <v>96602</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>224361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,17 +822,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>mötesplats väg Ö Björnaråsen, Vg</t>
+          <t>Björnareåsens NR, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>331681.7243208161</v>
+        <v>331579</v>
       </c>
       <c r="R3" t="n">
-        <v>6406633.11612391</v>
+        <v>6406504</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,34 +856,19 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-04-24</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-04-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>liten grupp i dikeskanten</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
@@ -892,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Aimon Niklasson</t>
+          <t>Tim Hipkiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Aimon Niklasson</t>
+          <t>Tim Hipkiss</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>87293074</v>
+        <v>92750691</v>
       </c>
       <c r="B4" t="n">
-        <v>96602</v>
+        <v>95519</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>224361</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,17 +929,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Björnareåsens NR, Vg</t>
+          <t>mötesplats väg Ö Björnaråsen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>331579</v>
+        <v>331681.7243208161</v>
       </c>
       <c r="R4" t="n">
-        <v>6406504</v>
+        <v>6406633.11612391</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,19 +963,34 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-08-05</t>
+          <t>2021-04-24</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-08-05</t>
+          <t>2021-04-24</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>liten grupp i dikeskanten</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
@@ -999,12 +999,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Aimon Niklasson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Aimon Niklasson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 14042-2023 artfynd.xlsx
+++ b/artfynd/A 14042-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>87293066</v>
       </c>
       <c r="B2" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>87293074</v>
+        <v>92750691</v>
       </c>
       <c r="B3" t="n">
-        <v>96602</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224361</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,17 +812,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Björnareåsens NR, Vg</t>
+          <t>mötesplats väg Ö Björnaråsen, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>331579</v>
+        <v>331682</v>
       </c>
       <c r="R3" t="n">
-        <v>6406504</v>
+        <v>6406633</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,19 +846,24 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-08-05</t>
+          <t>2021-04-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-08-05</t>
+          <t>2021-04-24</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>liten grupp i dikeskanten</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
@@ -877,137 +872,15 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Aimon Niklasson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Aimon Niklasson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>92750691</v>
-      </c>
-      <c r="B4" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>mötesplats väg Ö Björnaråsen, Vg</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>331681.7243208161</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6406633.11612391</v>
-      </c>
-      <c r="S4" t="n">
-        <v>25</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Partille</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Partille</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2021-04-24</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2021-04-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>liten grupp i dikeskanten</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Aimon Niklasson</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Aimon Niklasson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14042-2023 artfynd.xlsx
+++ b/artfynd/A 14042-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135039843</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87293066</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92750691</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135039067</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1215,6 +1240,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135039098</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1331,6 +1361,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135041178</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1438,8 +1473,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135039858</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 14042-2023 artfynd.xlsx
+++ b/artfynd/A 14042-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135039843</v>
       </c>
       <c r="B2" t="n">
-        <v>106199</v>
+        <v>106254</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>135039067</v>
       </c>
       <c r="B5" t="n">
-        <v>104332</v>
+        <v>104385</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>135039098</v>
       </c>
       <c r="B6" t="n">
-        <v>104332</v>
+        <v>104385</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>135041178</v>
       </c>
       <c r="B7" t="n">
-        <v>104332</v>
+        <v>104385</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>135039858</v>
       </c>
       <c r="B8" t="n">
-        <v>99504</v>
+        <v>99551</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 14042-2023 artfynd.xlsx
+++ b/artfynd/A 14042-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135039843</v>
       </c>
       <c r="B2" t="n">
-        <v>106254</v>
+        <v>106281</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>135039067</v>
       </c>
       <c r="B5" t="n">
-        <v>104385</v>
+        <v>104412</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>135039098</v>
       </c>
       <c r="B6" t="n">
-        <v>104385</v>
+        <v>104412</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>135041178</v>
       </c>
       <c r="B7" t="n">
-        <v>104385</v>
+        <v>104412</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>135039858</v>
       </c>
       <c r="B8" t="n">
-        <v>99551</v>
+        <v>99578</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 14042-2023 artfynd.xlsx
+++ b/artfynd/A 14042-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1369,10 +1369,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135039858</v>
+        <v>136555925</v>
       </c>
       <c r="B8" t="n">
-        <v>99578</v>
+        <v>104489</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,21 +1380,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222857</v>
+        <v>222395</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ekorrbär</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Maianthemum bifolium</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) F. W. Schmidt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1434,29 +1434,29 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="b">
         <v>0</v>
@@ -1475,7 +1475,231 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136555925</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135039858</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99578</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222857</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ekorrbär</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Maianthemum bifolium</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) F. W. Schmidt</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Björnaråsen, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>331575</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6406502</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Partille</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Partille</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135039858</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136555855</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98196</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Björnaråsen, Vg</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>331575</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6406502</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Partille</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Partille</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136555855</t>
         </is>
       </c>
     </row>
@@ -1488,6 +1712,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
